--- a/output/Tables/2019/Resampling/HIA_per_sex_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_sex_Rubin.xlsx
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,46 +534,46 @@
         </is>
       </c>
       <c r="C4">
-        <v>5589.351</v>
+        <v>4955.253</v>
       </c>
       <c r="D4">
-        <v>89.59</v>
+        <v>3092.462</v>
       </c>
       <c r="E4">
-        <v>11237.54</v>
+        <v>6799.247</v>
       </c>
       <c r="F4">
-        <v>9682.379999999999</v>
+        <v>4703.971</v>
       </c>
       <c r="G4">
-        <v>144.176</v>
+        <v>3015.47</v>
       </c>
       <c r="H4">
-        <v>19591.752</v>
+        <v>6362.578</v>
       </c>
       <c r="I4">
-        <v>82819394.352</v>
+        <v>275974736.726</v>
       </c>
       <c r="J4">
-        <v>1330913.695</v>
+        <v>172529506.676</v>
       </c>
       <c r="K4">
-        <v>166548477.05</v>
+        <v>378770723.411</v>
       </c>
       <c r="L4">
-        <v>1287655238.514</v>
+        <v>625614663.947</v>
       </c>
       <c r="M4">
-        <v>19230711.24</v>
+        <v>401471769.673</v>
       </c>
       <c r="N4">
-        <v>2608396605.097</v>
+        <v>846312682.0599999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -582,46 +582,46 @@
         </is>
       </c>
       <c r="C5">
-        <v>3847.913</v>
+        <v>6871.295</v>
       </c>
       <c r="D5">
-        <v>52.35</v>
+        <v>4467.533</v>
       </c>
       <c r="E5">
-        <v>7798.586</v>
+        <v>9309.314</v>
       </c>
       <c r="F5">
-        <v>3199.31</v>
+        <v>4495.329</v>
       </c>
       <c r="G5">
-        <v>44.108</v>
+        <v>2964.228</v>
       </c>
       <c r="H5">
-        <v>6490.949</v>
+        <v>6036.029</v>
       </c>
       <c r="I5">
-        <v>56958727.343</v>
+        <v>382764924.873</v>
       </c>
       <c r="J5">
-        <v>769699.887</v>
+        <v>249189544.317</v>
       </c>
       <c r="K5">
-        <v>115620188.006</v>
+        <v>518407473.926</v>
       </c>
       <c r="L5">
-        <v>425774148.137</v>
+        <v>597579954.993</v>
       </c>
       <c r="M5">
-        <v>5918231.333</v>
+        <v>393489921.129</v>
       </c>
       <c r="N5">
-        <v>862686940.806</v>
+        <v>800478814.642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,46 +630,46 @@
         </is>
       </c>
       <c r="C6">
-        <v>4954.481</v>
+        <v>5591.36</v>
       </c>
       <c r="D6">
-        <v>3094.126</v>
+        <v>89.672</v>
       </c>
       <c r="E6">
-        <v>6798.579</v>
+        <v>11225.642</v>
       </c>
       <c r="F6">
-        <v>4706.698</v>
+        <v>9682.803</v>
       </c>
       <c r="G6">
-        <v>3015.649</v>
+        <v>145.062</v>
       </c>
       <c r="H6">
-        <v>6360.772</v>
+        <v>19607.474</v>
       </c>
       <c r="I6">
-        <v>275796316.027</v>
+        <v>82760299.287</v>
       </c>
       <c r="J6">
-        <v>172273602.516</v>
+        <v>1327198.016</v>
       </c>
       <c r="K6">
-        <v>378736937.309</v>
+        <v>166454493.094</v>
       </c>
       <c r="L6">
-        <v>625782131.9220001</v>
+        <v>1286748460.301</v>
       </c>
       <c r="M6">
-        <v>401037875.911</v>
+        <v>19212501.689</v>
       </c>
       <c r="N6">
-        <v>845552452.594</v>
+        <v>2607117986.191</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>6870.237</v>
+        <v>3845.125</v>
       </c>
       <c r="D7">
-        <v>4478.716</v>
+        <v>51.625</v>
       </c>
       <c r="E7">
-        <v>9307.527</v>
+        <v>7793.318</v>
       </c>
       <c r="F7">
-        <v>4493.498</v>
+        <v>3201.082</v>
       </c>
       <c r="G7">
-        <v>2959.146</v>
+        <v>44.192</v>
       </c>
       <c r="H7">
-        <v>6027.035</v>
+        <v>6482.162</v>
       </c>
       <c r="I7">
-        <v>382597042.773</v>
+        <v>56923614.509</v>
       </c>
       <c r="J7">
-        <v>248650309.773</v>
+        <v>770449.4399999999</v>
       </c>
       <c r="K7">
-        <v>518290081.387</v>
+        <v>115271074.887</v>
       </c>
       <c r="L7">
-        <v>597766487.842</v>
+        <v>425935536.273</v>
       </c>
       <c r="M7">
-        <v>394053163.739</v>
+        <v>5897034.843</v>
       </c>
       <c r="N7">
-        <v>801814299.979</v>
+        <v>863886876.656</v>
       </c>
     </row>
     <row r="8">
